--- a/Unity/Assets/Config/Excel/Skill/SkillDamageConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/SkillDamageConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -22,10 +22,10 @@
     <t>伤害类型</t>
   </si>
   <si>
-    <t>Numeric伤害加成比例</t>
-  </si>
-  <si>
-    <t>基础伤害</t>
+    <t>伤害系数。基础伤害  = 攻击力 * 伤害系数 + 固定伤害值 = 攻击力 * Coefficient + BaseValue</t>
+  </si>
+  <si>
+    <t>技能固定伤害值</t>
   </si>
   <si>
     <t>是否可暴击,1可以</t>
@@ -34,6 +34,21 @@
     <t>吸血比例</t>
   </si>
   <si>
+    <t>0:立即触发，1：延迟，2：持续伤害</t>
+  </si>
+  <si>
+    <t>延迟伤害执行时间，单位毫秒</t>
+  </si>
+  <si>
+    <t>命中时自身添加的BuffID</t>
+  </si>
+  <si>
+    <t>命中时队友添加的BuffID</t>
+  </si>
+  <si>
+    <t>命中时目标添加的BuffID</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -43,16 +58,31 @@
     <t>DamageType</t>
   </si>
   <si>
-    <t>NumericRatio</t>
-  </si>
-  <si>
-    <t>FlatBaseValue</t>
+    <t>Coefficient</t>
+  </si>
+  <si>
+    <t>BaseDamage</t>
   </si>
   <si>
     <t>CanCrit</t>
   </si>
   <si>
-    <t>LifestealRate</t>
+    <t>LifeStealRate</t>
+  </si>
+  <si>
+    <t>DamageTriggerType</t>
+  </si>
+  <si>
+    <t>DelayTime</t>
+  </si>
+  <si>
+    <t>HitBuffIdsForSelf</t>
+  </si>
+  <si>
+    <t>HitBuffIdsForTeam</t>
+  </si>
+  <si>
+    <t>HitBuffIdsForTarget</t>
   </si>
   <si>
     <t>int</t>
@@ -62,6 +92,9 @@
   </si>
   <si>
     <t>double</t>
+  </si>
+  <si>
+    <t>int[]</t>
   </si>
   <si>
     <t>1</t>
@@ -1479,17 +1512,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6719" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1719" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.35156" style="1" customWidth="1"/>
-    <col min="8" max="9" width="14.8516" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.2422" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.3516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6719" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.4375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1719" style="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22.6719" style="1" customWidth="1"/>
+    <col min="12" max="12" width="22.2188" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.1797" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.5156" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1502,6 +1541,11 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1513,6 +1557,11 @@
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" ht="14" customHeight="1">
       <c r="A3" s="2"/>
@@ -1538,131 +1587,191 @@
       <c r="I3" t="s" s="8">
         <v>6</v>
       </c>
+      <c r="J3" t="s" s="8">
+        <v>7</v>
+      </c>
+      <c r="K3" t="s" s="8">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s" s="8">
+        <v>9</v>
+      </c>
+      <c r="M3" t="s" s="8">
+        <v>10</v>
+      </c>
+      <c r="N3" t="s" s="8">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="9"/>
       <c r="B4" s="10"/>
       <c r="C4" t="s" s="5">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s" s="11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s" s="5">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s" s="7">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s" s="8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s" s="8">
-        <v>13</v>
+        <v>18</v>
+      </c>
+      <c r="J4" t="s" s="8">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s" s="8">
+        <v>20</v>
+      </c>
+      <c r="L4" t="s" s="8">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s" s="8">
+        <v>22</v>
+      </c>
+      <c r="N4" t="s" s="8">
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="4"/>
       <c r="C5" t="s" s="5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s" s="5">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s" s="5">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s" s="12">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s" s="7">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s" s="7">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s" s="7">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="J5" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s" s="7">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s" s="7">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s" s="7">
+        <v>27</v>
+      </c>
+      <c r="N5" t="s" s="7">
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="13">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s" s="14">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s" s="13">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s" s="13">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s" s="13">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s" s="13">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I6" t="s" s="13">
-        <v>21</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s" s="15">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s" s="15">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="16"/>
@@ -1674,6 +1783,11 @@
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
       <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="20"/>
@@ -1685,6 +1799,11 @@
       <c r="G10" s="21"/>
       <c r="H10" s="22"/>
       <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
